--- a/Server Hardware/Bill Of Materials.xlsx
+++ b/Server Hardware/Bill Of Materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atlantictu-my.sharepoint.com/personal/l00187849_atu_ie/Documents/L00187849/L00187849/Hybrid Cloud/CA1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A80381A-F444-4131-A807-C30B0AD0644D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{6A80381A-F444-4131-A807-C30B0AD0644D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8955036F-AC44-4E50-9CE1-68681E58A1B3}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{29C7FB07-4F41-45E8-9437-14057472432A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{29C7FB07-4F41-45E8-9437-14057472432A}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill Of Materials" sheetId="1" r:id="rId1"/>
@@ -359,9 +359,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
-    <t>Priced Bill of Materials – Server Hardware Assignment</t>
-  </si>
-  <si>
     <t>VAT Rate</t>
   </si>
   <si>
@@ -552,6 +549,9 @@
   </si>
   <si>
     <t>Equipment &amp; Labour after VAT</t>
+  </si>
+  <si>
+    <t>Priced Bill of Materials</t>
   </si>
 </sst>
 </file>
@@ -680,131 +680,131 @@
   </cellStyleXfs>
   <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1141,790 +1141,790 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B79A1F0-DD1E-42BB-A051-C5EF254FF080}">
   <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24" style="5" customWidth="1"/>
-    <col min="2" max="2" width="42" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12" style="5" customWidth="1"/>
-    <col min="4" max="4" width="16" style="5" customWidth="1"/>
-    <col min="5" max="5" width="20" style="5" customWidth="1"/>
-    <col min="6" max="6" width="14" style="5" customWidth="1"/>
-    <col min="7" max="7" width="20" style="5" customWidth="1"/>
-    <col min="8" max="8" width="55" style="5" customWidth="1"/>
+    <col min="1" max="1" width="24" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20" style="1" customWidth="1"/>
+    <col min="8" max="8" width="55" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+    </row>
+    <row r="2" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>0.23</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="C5" s="7">
         <v>1</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>1399</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <f>C5*D5</f>
         <v>1399</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="9">
         <f>E5*$B$2</f>
         <v>321.77000000000004</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="9">
         <f>E5+F5</f>
         <v>1720.77</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <v>8</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="8">
         <v>35</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <f>C6*D6</f>
         <v>280</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="9">
         <f>E6*$B$2</f>
         <v>64.400000000000006</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="9">
         <f>E6+F6</f>
         <v>344.4</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <v>2</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="12">
         <v>89</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="13">
         <f>C7*D7</f>
         <v>178</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="13">
         <f>E7*$B$2</f>
         <v>40.940000000000005</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="13">
         <f>E7+F7</f>
         <v>218.94</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>1</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <v>1299</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="13">
         <f>C8*D8</f>
         <v>1299</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="13">
         <f>E8*$B$2</f>
         <v>298.77000000000004</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="13">
         <f>E8+F8</f>
         <v>1597.77</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="B10" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="21">
+      <c r="C10" s="19">
         <v>2</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <v>60000</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="21">
         <f>C10*D10</f>
         <v>120000</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="21">
         <f>E10*$B$2</f>
         <v>27600</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="21">
         <f>E10+F10</f>
         <v>147600</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="21">
+      <c r="C11" s="19">
         <v>2</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="20">
         <v>1500</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="21">
         <f>C11*D11</f>
         <v>3000</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="21">
         <f>E11*$B$2</f>
         <v>690</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="21">
         <f>E11+F11</f>
         <v>3690</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="21">
+      <c r="C12" s="19">
         <v>8</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="20">
         <v>500</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="21">
         <f>C12*D12</f>
         <v>4000</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="21">
         <f>E12*$B$2</f>
         <v>920</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="21">
         <f>E12+F12</f>
         <v>4920</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="21">
+      <c r="C13" s="19">
         <v>2</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <v>800</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="21">
         <f>C13*D13</f>
         <v>1600</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="21">
         <f>E13*$B$2</f>
         <v>368</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="21">
         <f>E13+F13</f>
         <v>1968</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="16"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="B15" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="C15" s="23">
         <v>2</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="24">
         <v>1680</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="25">
         <f>C15*D15</f>
         <v>3360</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="25">
         <f>E15*$B$2</f>
         <v>772.80000000000007</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="25">
         <f>E15+F15</f>
         <v>4132.8</v>
       </c>
-      <c r="H15" s="24" t="s">
+      <c r="H15" s="22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="25">
+      <c r="C16" s="23">
         <v>1</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="24">
         <v>619.13</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="25">
         <f>C16*D16</f>
         <v>619.13</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="25">
         <f>E16*$B$2</f>
         <v>142.3999</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="25">
         <f>E16+F16</f>
         <v>761.5299</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="B18" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="29">
+      <c r="C18" s="27">
         <v>6</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="28">
         <v>15</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="29">
         <f>C18*D18</f>
         <v>90</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="29">
         <f>E18*$B$2</f>
         <v>20.7</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="29">
         <f>E18+F18</f>
         <v>110.7</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H18" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="26" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="29">
+      <c r="C19" s="27">
         <v>6</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="28">
         <v>18</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="29">
         <f>C19*D19</f>
         <v>108</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="29">
         <f>E19*$B$2</f>
         <v>24.84</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="29">
         <f>E19+F19</f>
         <v>132.84</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="H19" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="26" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="29">
+      <c r="C20" s="27">
         <v>48</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="28">
         <v>5</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="29">
         <f>C20*D20</f>
         <v>240</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="29">
         <f>E20*$B$2</f>
         <v>55.2</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="29">
         <f>E20+F20</f>
         <v>295.2</v>
       </c>
-      <c r="H20" s="28" t="s">
+      <c r="H20" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="26" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="29">
+      <c r="C21" s="27">
         <v>8</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="28">
         <v>65</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="29">
         <f>C21*D21</f>
         <v>520</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="29">
         <f>E21*$B$2</f>
         <v>119.60000000000001</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="29">
         <f>E21+F21</f>
         <v>639.6</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="H21" s="26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="29">
+      <c r="C22" s="27">
         <v>1</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="28">
         <v>450</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="29">
         <f>C22*D22</f>
         <v>450</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="29">
         <f>E22*$B$2</f>
         <v>103.5</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="29">
         <f>E22+F22</f>
         <v>553.5</v>
       </c>
-      <c r="H22" s="28" t="s">
+      <c r="H22" s="26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="30" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="16"/>
-    </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="32" t="s">
+      <c r="B24" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="33">
+      <c r="C24" s="31">
         <v>2</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="32">
         <v>6000</v>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="33">
         <f>C24*D24</f>
         <v>12000</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="33">
         <f>E24*$B$2</f>
         <v>2760</v>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="33">
         <f>E24+F24</f>
         <v>14760</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" s="30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="30" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="33">
+      <c r="C25" s="31">
         <v>1</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="32">
         <v>2500</v>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="33">
         <f>C25*D25</f>
         <v>2500</v>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="33">
         <f>E25*$B$2</f>
         <v>575</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="33">
         <f>E25+F25</f>
         <v>3075</v>
       </c>
-      <c r="H25" s="32" t="s">
+      <c r="H25" s="30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="14"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="34" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="16"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
+      <c r="B27" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="37">
+      <c r="C27" s="35">
         <v>16</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="36">
         <v>65</v>
       </c>
-      <c r="E27" s="39">
+      <c r="E27" s="37">
         <f>C27*D27</f>
         <v>1040</v>
       </c>
-      <c r="F27" s="39">
+      <c r="F27" s="37">
         <f>E27*$B$2</f>
         <v>239.20000000000002</v>
       </c>
-      <c r="G27" s="39">
+      <c r="G27" s="37">
         <f>E27+F27</f>
         <v>1279.2</v>
       </c>
-      <c r="H27" s="36" t="s">
+      <c r="H27" s="34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="34" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="37">
+      <c r="C28" s="35">
         <v>12</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="36">
         <v>75</v>
       </c>
-      <c r="E28" s="39">
+      <c r="E28" s="37">
         <f>C28*D28</f>
         <v>900</v>
       </c>
-      <c r="F28" s="39">
+      <c r="F28" s="37">
         <f>E28*$B$2</f>
         <v>207</v>
       </c>
-      <c r="G28" s="39">
+      <c r="G28" s="37">
         <f>E28+F28</f>
         <v>1107</v>
       </c>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="34" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="37">
+      <c r="C29" s="35">
         <v>8</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="36">
         <v>75</v>
       </c>
-      <c r="E29" s="39">
+      <c r="E29" s="37">
         <f>C29*D29</f>
         <v>600</v>
       </c>
-      <c r="F29" s="39">
+      <c r="F29" s="37">
         <f>E29*$B$2</f>
         <v>138</v>
       </c>
-      <c r="G29" s="39">
+      <c r="G29" s="37">
         <f>E29+F29</f>
         <v>738</v>
       </c>
-      <c r="H29" s="36" t="s">
+      <c r="H29" s="34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="34" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="37">
+      <c r="C30" s="35">
         <v>6</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="36">
         <v>65</v>
       </c>
-      <c r="E30" s="39">
+      <c r="E30" s="37">
         <f>C30*D30</f>
         <v>390</v>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="37">
         <f>E30*$B$2</f>
         <v>89.7</v>
       </c>
-      <c r="G30" s="39">
+      <c r="G30" s="37">
         <f>E30+F30</f>
         <v>479.7</v>
       </c>
-      <c r="H30" s="36" t="s">
+      <c r="H30" s="34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="14"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="38" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="16"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="40" t="s">
+      <c r="B32" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42">
+      <c r="C32" s="39"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40">
         <f>SUM(E5:E30)</f>
         <v>154573.13</v>
       </c>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="40"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42">
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="38"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="39"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40">
         <f>SUM(F5:F30)</f>
         <v>35551.819899999995</v>
       </c>
-      <c r="G33" s="42"/>
-      <c r="H33" s="40"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42">
+      <c r="G33" s="40"/>
+      <c r="H33" s="38"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="39"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40">
         <f>SUM(G5:G30)</f>
         <v>190124.94990000004</v>
       </c>
-      <c r="H34" s="40"/>
+      <c r="H34" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="1">
